--- a/templates/hlb-connectfirst.xlsx
+++ b/templates/hlb-connectfirst.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,16 +30,55 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF33CCCC"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +86,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,95 +484,95 @@
   <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
+    <col min="1" max="1" width="17.83" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="19.5" customWidth="1"/>
+    <col min="4" max="4" width="30.5" customWidth="1"/>
+    <col min="5" max="5" width="11.16" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="7" max="7" width="22.66" customWidth="1"/>
+    <col min="8" max="8" width="22.66" customWidth="1"/>
+    <col min="9" max="9" width="15.16" customWidth="1"/>
+    <col min="10" max="10" width="22.5" customWidth="1"/>
+    <col min="11" max="11" width="17.16" customWidth="1"/>
+    <col min="12" max="12" width="25" customWidth="1"/>
+    <col min="13" max="13" width="22.5" customWidth="1"/>
+    <col min="14" max="14" width="22.5" customWidth="1"/>
+    <col min="15" max="15" width="41.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="96" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>*Payment Mode</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>*Beneficiary Bank Code    Refer to Bank Code (IBG)/ (RENTAS) / (DuitNow) sheet</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>*Beneficiary Account No. FT: 11 Digits                            IBG: 5 to 17 Digits                   RENTAS: 5 to 17 Digits                            DuitNow: 34 Alphanumeric</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>*Beneficiary Name                             FT - Maximum length 70 char                         IBG - Maximum length 20 char                     RENTAS - Maximum length 70 char                     DuitNow: Maximum length 140 char</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>*Currency (MYR)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>*Amount               FT: Any amount             IBG: Max RM1Mil                     RENTAS: Min RM10K                     DuitNow: Max RM10Mil</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>*Recipient Reference Maximum length 20                DuitNow: Maximum length 40 char</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Other Payment Details Maximum length 20                              DuitNow: Maximum length 140 char</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>*ID Validation (Y/N)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Validation ID Type  (Please refer to File specification for more details)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Validation ID Value New IC: 12 digits        Old IC: 7 to 8 char  Others: Max 20 char         Passport No: 20 char</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Transaction Type (applicable for Payment Type = RENTAS only)                Possible Value: TPT</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Transaction Code (applicable for Payment Type = RENTAS only)                    Possible Value: IFT03</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Purpose Of Transfer (applicable for Payment Type = RENTAS only)     Possible Value: Cash</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Beneficiary Email Address Maximum length 150</t>
         </is>
